--- a/digital-products/pr-readiness-audit/singapore-pr-readiness-document-audit-2026.xlsx
+++ b/digital-products/pr-readiness-audit/singapore-pr-readiness-document-audit-2026.xlsx
@@ -433,7 +433,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="S$#,##0"/>
+    <numFmt numFmtId="164" formatCode="&quot;S$&quot;#,##0"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
   <fonts count="16" x14ac:knownFonts="1">
